--- a/schoolDocs/Nursery_ImportReady.xlsx
+++ b/schoolDocs/Nursery_ImportReady.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="57">
   <si>
     <t>Sr No</t>
   </si>
@@ -50,6 +50,9 @@
     <t>Already Collected (Rs)</t>
   </si>
   <si>
+    <t>Admission Date (DD/MM/YYYY)</t>
+  </si>
+  <si>
     <t>Village</t>
   </si>
   <si>
@@ -92,6 +95,9 @@
     <t>general</t>
   </si>
   <si>
+    <t>04/12/2024</t>
+  </si>
+  <si>
     <t>Chaufula</t>
   </si>
   <si>
@@ -104,6 +110,9 @@
     <t>rte</t>
   </si>
   <si>
+    <t>21/01/2025</t>
+  </si>
+  <si>
     <t>Varvand</t>
   </si>
   <si>
@@ -122,6 +131,9 @@
     <t>Rajvir Khanderao Devkar</t>
   </si>
   <si>
+    <t>02/12/2024</t>
+  </si>
+  <si>
     <t>Kedgaon</t>
   </si>
   <si>
@@ -131,12 +143,18 @@
     <t>discount</t>
   </si>
   <si>
+    <t>29/01/2025</t>
+  </si>
+  <si>
     <t>Aaradhya Devidas Kalapahad</t>
   </si>
   <si>
     <t>female</t>
   </si>
   <si>
+    <t>20/01/2025</t>
+  </si>
+  <si>
     <t>Baravkarvadi</t>
   </si>
   <si>
@@ -149,16 +167,22 @@
     <t>Sukanya Hake</t>
   </si>
   <si>
+    <t>26/12/2024</t>
+  </si>
+  <si>
     <t>Khutbav</t>
   </si>
   <si>
     <t>10km</t>
   </si>
   <si>
-    <t>Custom fee ₹2500 — collected ₹0, full amount outstanding</t>
+    <t>Custom fee ₹2500 — collected ₹0 outstanding</t>
   </si>
   <si>
     <t>Sanchita Gautam</t>
+  </si>
+  <si>
+    <t>13/01/2025</t>
   </si>
   <si>
     <t>100% discount — confirm with admin</t>
@@ -198,7 +222,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -223,6 +247,12 @@
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD5EAD0"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -236,7 +266,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" shrinkToFit="false"/>
@@ -245,6 +275,9 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="2" numFmtId="0" fillId="4" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="5" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="0" numFmtId="0" fillId="4" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0"/>
@@ -547,7 +580,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:T8"/>
+  <dimension ref="A1:U8"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="9.283" bestFit="true" customWidth="true" style="0"/>
@@ -561,18 +594,19 @@
     <col min="9" max="9" width="15.139" bestFit="true" customWidth="true" style="0"/>
     <col min="10" max="10" width="24.565" bestFit="true" customWidth="true" style="0"/>
     <col min="11" max="11" width="29.279" bestFit="true" customWidth="true" style="0"/>
-    <col min="12" max="12" width="15.282" bestFit="true" customWidth="true" style="0"/>
-    <col min="13" max="13" width="26.993" bestFit="true" customWidth="true" style="0"/>
-    <col min="14" max="14" width="16.282" bestFit="true" customWidth="true" style="0"/>
-    <col min="15" max="15" width="23.423" bestFit="true" customWidth="true" style="0"/>
-    <col min="16" max="16" width="16.282" bestFit="true" customWidth="true" style="0"/>
-    <col min="17" max="17" width="23.423" bestFit="true" customWidth="true" style="0"/>
-    <col min="18" max="18" width="15.139" bestFit="true" customWidth="true" style="0"/>
-    <col min="19" max="19" width="22.28" bestFit="true" customWidth="true" style="0"/>
-    <col min="20" max="20" width="67.127" bestFit="true" customWidth="true" style="0"/>
+    <col min="12" max="12" width="35.277" bestFit="true" customWidth="true" style="0"/>
+    <col min="13" max="13" width="15.282" bestFit="true" customWidth="true" style="0"/>
+    <col min="14" max="14" width="26.993" bestFit="true" customWidth="true" style="0"/>
+    <col min="15" max="15" width="16.282" bestFit="true" customWidth="true" style="0"/>
+    <col min="16" max="16" width="23.423" bestFit="true" customWidth="true" style="0"/>
+    <col min="17" max="17" width="16.282" bestFit="true" customWidth="true" style="0"/>
+    <col min="18" max="18" width="23.423" bestFit="true" customWidth="true" style="0"/>
+    <col min="19" max="19" width="15.139" bestFit="true" customWidth="true" style="0"/>
+    <col min="20" max="20" width="22.28" bestFit="true" customWidth="true" style="0"/>
+    <col min="21" max="21" width="52.844" bestFit="true" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" customHeight="1" ht="30">
+    <row r="1" spans="1:21" customHeight="1" ht="30">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -606,7 +640,7 @@
       <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="4" t="s">
         <v>11</v>
       </c>
       <c r="M1" s="1" t="s">
@@ -630,133 +664,145 @@
       <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
+      <c r="U1" s="2" t="s">
+        <v>20</v>
+      </c>
     </row>
-    <row r="2" spans="1:20">
+    <row r="2" spans="1:21">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G2">
         <v>9561305558</v>
       </c>
       <c r="H2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K2">
         <v>5000</v>
       </c>
       <c r="L2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M2" t="s">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="N2" t="s">
+        <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:20">
+    <row r="3" spans="1:21">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G3">
         <v>8830578600</v>
       </c>
       <c r="H3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="M3" t="s">
-        <v>30</v>
-      </c>
-      <c r="O3" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q3" t="s">
         <v>32</v>
       </c>
-      <c r="T3" t="s">
+      <c r="N3" t="s">
         <v>33</v>
       </c>
+      <c r="P3" t="s">
+        <v>34</v>
+      </c>
+      <c r="R3" t="s">
+        <v>35</v>
+      </c>
+      <c r="U3" t="s">
+        <v>36</v>
+      </c>
     </row>
-    <row r="4" spans="1:20">
+    <row r="4" spans="1:21">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G4">
         <v>9307141201</v>
       </c>
       <c r="H4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K4">
         <v>16200</v>
       </c>
       <c r="L4" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="M4" t="s">
-        <v>30</v>
+        <v>39</v>
+      </c>
+      <c r="N4" t="s">
+        <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:20">
+    <row r="5" spans="1:21">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G5">
         <v>9022585878</v>
       </c>
       <c r="H5" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="I5">
         <v>50</v>
@@ -764,28 +810,31 @@
       <c r="K5">
         <v>2000</v>
       </c>
+      <c r="L5" t="s">
+        <v>42</v>
+      </c>
     </row>
-    <row r="6" spans="1:20">
+    <row r="6" spans="1:21">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D6" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G6">
         <v>7972024744</v>
       </c>
       <c r="H6" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="I6">
         <v>50</v>
@@ -793,83 +842,92 @@
       <c r="J6">
         <v>6000</v>
       </c>
-      <c r="K6" s="4">
+      <c r="K6" s="5">
         <v>6000</v>
       </c>
       <c r="L6" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="M6" t="s">
-        <v>41</v>
-      </c>
-      <c r="O6" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>32</v>
-      </c>
-      <c r="T6" s="4"/>
+        <v>46</v>
+      </c>
+      <c r="N6" t="s">
+        <v>47</v>
+      </c>
+      <c r="P6" t="s">
+        <v>48</v>
+      </c>
+      <c r="R6" t="s">
+        <v>35</v>
+      </c>
+      <c r="U6" s="5"/>
     </row>
-    <row r="7" spans="1:20">
+    <row r="7" spans="1:21">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="D7" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G7">
         <v>7397973646</v>
       </c>
       <c r="H7" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="J7">
         <v>2500</v>
       </c>
-      <c r="K7" s="4"/>
+      <c r="K7" s="5"/>
       <c r="L7" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="M7" t="s">
-        <v>45</v>
-      </c>
-      <c r="T7" s="4" t="s">
-        <v>46</v>
+        <v>51</v>
+      </c>
+      <c r="N7" t="s">
+        <v>52</v>
+      </c>
+      <c r="U7" s="5" t="s">
+        <v>53</v>
       </c>
     </row>
-    <row r="8" spans="1:20">
+    <row r="8" spans="1:21">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="D8" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H8" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="I8">
         <v>100</v>
       </c>
-      <c r="T8" t="s">
-        <v>48</v>
+      <c r="L8" t="s">
+        <v>55</v>
+      </c>
+      <c r="U8" t="s">
+        <v>56</v>
       </c>
     </row>
   </sheetData>
